--- a/resources/templates/standard/A8101-03.xlsx
+++ b/resources/templates/standard/A8101-03.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>[팬더믹] 비상사태 대비 훈련 평가표</t>
   </si>
@@ -647,10 +650,12 @@
     </row>
     <row r="2" ht="23.1" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="3"/>
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="C2" s="3"/>
       <c r="D2" s="4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -658,10 +663,10 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="23.45" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -675,26 +680,26 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" ht="30.95" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -706,7 +711,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -723,7 +728,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -740,7 +745,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -757,7 +762,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -774,7 +779,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
@@ -791,7 +796,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
@@ -808,7 +813,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -825,7 +830,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -842,7 +847,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -859,7 +864,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
@@ -874,7 +879,7 @@
       <c r="A15" s="1"/>
       <c r="B15" s="12"/>
       <c r="C15" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
@@ -883,7 +888,7 @@
         <f>SUM(G5:G14)</f>
       </c>
       <c r="H15" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
@@ -892,7 +897,7 @@
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" s="16"/>
       <c r="D16" s="16"/>
